--- a/dados/excel/genero_geral.xlsx
+++ b/dados/excel/genero_geral.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cobertura gênero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura gênero" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$H$4</definedName>
@@ -638,7 +638,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/genero_geral.xlsx
+++ b/dados/excel/genero_geral.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -879,25 +879,25 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>659300</v>
+        <v>655773</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>20973</v>
+        <v>20858</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>4146801033</v>
+        <v>4124876292.88</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>6289.702765053845</v>
+        <v>6290.097782128877</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>4601.55</v>
+        <v>4604.41</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>78.34</v>
+        <v>77.91</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>69.27</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -907,25 +907,25 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>195038</v>
+        <v>193648</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>5482</v>
+        <v>5436</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1755223989.31</v>
+        <v>1744381234.67</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>8999.394934884484</v>
+        <v>9008.000261660332</v>
       </c>
       <c r="F3" s="14" t="n">
         <v>6480.15</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.48</v>
+        <v>20.3</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>29.32</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="4">
@@ -935,25 +935,25 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>11434</v>
+        <v>16351</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>317</v>
+        <v>478</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>84602701.22</v>
+        <v>117370195.98</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>7399.221726429946</v>
+        <v>7178.166227142071</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>5539.21</v>
+        <v>5274.63</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1.18</v>
+        <v>1.79</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
     </row>
   </sheetData>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>26455</v>
+        <v>26294</v>
       </c>
     </row>
     <row r="5">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>317</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>20973</v>
+        <v>20858</v>
       </c>
     </row>
     <row r="7">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>5482</v>
+        <v>5436</v>
       </c>
     </row>
     <row r="8">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>98.81999999999999</v>
+        <v>98.20999999999999</v>
       </c>
     </row>
   </sheetData>
